--- a/01-Test-Cases/Pacientes_Test_Cases.xlsx
+++ b/01-Test-Cases/Pacientes_Test_Cases.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lucas\Desktop\Trabajos Personal\Excel de trabajos personales\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lucas\Desktop\Trabajos Personal\QA-testing-gestion-turnos-medicos\01-Test-Cases\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{093ED3E1-EACE-46D7-92DC-9957D85CF53C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D48803B-6722-4056-BA63-16535480B31E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{21F9C2CD-0365-49D1-9516-5EA4AC8F9364}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="97">
   <si>
     <t>Proyecto</t>
   </si>
@@ -102,114 +102,18 @@
     <t>RF-015</t>
   </si>
   <si>
-    <t>TC-LOGIN-001</t>
-  </si>
-  <si>
     <t>Alta</t>
   </si>
   <si>
-    <t>El sistema autentica al usuario y muestra la pantalla principal según el rol asignado.</t>
-  </si>
-  <si>
     <t>Pendiente</t>
   </si>
   <si>
     <t>Ninguna</t>
   </si>
   <si>
-    <t>TC-LOGIN-002</t>
-  </si>
-  <si>
-    <t>El sistema rechaza la autenticación y muestra un mensaje indicando que las credenciales son incorrectas.</t>
-  </si>
-  <si>
-    <t>TC-LOGIN-003</t>
-  </si>
-  <si>
-    <t>El sistema rechaza la autenticación y muestra un mensaje indicando que el usuario o la contraseña son incorrectos.</t>
-  </si>
-  <si>
-    <t>TC-LOGIN-004</t>
-  </si>
-  <si>
     <t>Media</t>
   </si>
   <si>
-    <t>El sistema procesa el usuario según la regla definida para espacios en blanco y permite o rechaza el acceso de acuerdo con esa especificación</t>
-  </si>
-  <si>
-    <t>TC-LOGIN-005</t>
-  </si>
-  <si>
-    <t>TC-LOGIN-006</t>
-  </si>
-  <si>
-    <t>El sistema muestra un mensaje indicando que los campos estan vacíos.</t>
-  </si>
-  <si>
-    <t>TC-LOGIN-007</t>
-  </si>
-  <si>
-    <t>El sistema muestra un mensaje indicando que el campo "Usuario" esta vacío y rechaza la autenticación.</t>
-  </si>
-  <si>
-    <t>TC-LOGIN-008</t>
-  </si>
-  <si>
-    <t>El sistema muestra un mensaje indicando que el campo "Constraseña" esta vacío y rechaza la autenticación.</t>
-  </si>
-  <si>
-    <t>TC-LOGIN-009</t>
-  </si>
-  <si>
-    <t>El sistema cierra la sesión del usuario y redirige a la pantalla de inicio de sesión.</t>
-  </si>
-  <si>
-    <t>TC-LOGIN-010</t>
-  </si>
-  <si>
-    <t>El sistema impide el acceso y redirige al usuario a la pantalla de inicio de sesión o muestra un mensaje indicando que debe autenticarse.</t>
-  </si>
-  <si>
-    <t>TC-LOGIN-011</t>
-  </si>
-  <si>
-    <t>El sistema valida la longitud del campo usuario y muestra un mensaje de error o impide ingresar más caracteres, según la especificación.</t>
-  </si>
-  <si>
-    <t>TC-LOGIN-012</t>
-  </si>
-  <si>
-    <t>El sistema valida la longitud del campo contraseña y muestra un mensaje de error o impide ingresar más caracteres, según la especificación.</t>
-  </si>
-  <si>
-    <t>TC-LOGIN-013</t>
-  </si>
-  <si>
-    <t>Los caracteres ingresados en el campo contraseña se muestran ocultos (por ejemplo, mediante puntos o asteriscos) para proteger la información del usuario.</t>
-  </si>
-  <si>
-    <t>TC-LOGIN-014</t>
-  </si>
-  <si>
-    <t>El sistema inicia sesión correctamente y muestra la pantalla principal del usuario.</t>
-  </si>
-  <si>
-    <t>TC-LOGIN-015</t>
-  </si>
-  <si>
-    <t>El sistema muestra un mensaje de error claro e informativo indicando que las credenciales ingresadas son incorrectas, sin revelar información sensible sobre la existencia del usuario.</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> </t>
-  </si>
-  <si>
-    <t xml:space="preserve">    </t>
-  </si>
-  <si>
-    <t xml:space="preserve">      </t>
-  </si>
-  <si>
     <t>Registrar un paciente con todos los datos válidos</t>
   </si>
   <si>
@@ -246,23 +150,223 @@
     <t>Eliminar correctamente un paciente existente</t>
   </si>
   <si>
-    <t>Verificar que los campos obligatorios estén identificados correctamente</t>
-  </si>
-  <si>
-    <t>Verificar que el sistema muestre un mensaje de confirmación al registrar un paciente</t>
-  </si>
-  <si>
-    <t>Verificar que el sistema muestre un mensaje de confirmación al eliminar un paciente</t>
-  </si>
-  <si>
     <t>Pacientes</t>
+  </si>
+  <si>
+    <t>Baja</t>
+  </si>
+  <si>
+    <t>TC-PAC-001</t>
+  </si>
+  <si>
+    <t>TC-PAC-002</t>
+  </si>
+  <si>
+    <t>TC-PAC-003</t>
+  </si>
+  <si>
+    <t>TC-PAC-004</t>
+  </si>
+  <si>
+    <t>TC-PAC-005</t>
+  </si>
+  <si>
+    <t>TC-PAC-006</t>
+  </si>
+  <si>
+    <t>TC-PAC-007</t>
+  </si>
+  <si>
+    <t>TC-PAC-008</t>
+  </si>
+  <si>
+    <t>TC-PAC-009</t>
+  </si>
+  <si>
+    <t>TC-PAC-010</t>
+  </si>
+  <si>
+    <t>TC-PAC-011</t>
+  </si>
+  <si>
+    <t>TC-PAC-012</t>
+  </si>
+  <si>
+    <t>TC-PAC-013</t>
+  </si>
+  <si>
+    <t>TC-PAC-014</t>
+  </si>
+  <si>
+    <t>TC-PAC-015</t>
+  </si>
+  <si>
+    <t>RF-001</t>
+  </si>
+  <si>
+    <t>RF-002</t>
+  </si>
+  <si>
+    <t>Verificar que los campos obligatorios se encuentren correctamente identificados en el formulario.</t>
+  </si>
+  <si>
+    <t>Verificar que el sistema confirme el registro exitoso de un paciente.</t>
+  </si>
+  <si>
+    <t>Verificar que el sistema confirme la eliminación exitosa de un paciente.</t>
+  </si>
+  <si>
+    <t>TC-PAC-001, 002, 003, 004, 005, 006, 012, 014, 015</t>
+  </si>
+  <si>
+    <t>Casos Asociados</t>
+  </si>
+  <si>
+    <t>TC-PAC-007, 008, 009, 010, 011, 013</t>
+  </si>
+  <si>
+    <t>El usuario debe haber iniciado sesión y contar con permisos para gestionar pacientes.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 1. Acceder al módulo Pacientes.
+2. Presionar Nuevo Paciente.
+3. Completar Nombre, Apellido, DNI, Obra Social, Correo y Teléfono con datos válidos.
+4. Presionar Guardar.</t>
+  </si>
+  <si>
+    <t>El sistema registra correctamente al paciente y muestra un mensaje de confirmación.</t>
+  </si>
+  <si>
+    <t>Debe existir un paciente registrado.</t>
+  </si>
+  <si>
+    <t>1. Acceder al módulo Pacientes.
+2. Buscar un paciente existente.
+3. Seleccionar Editar.
+4. Modificar uno o más datos.
+5. Presionar Guardar.</t>
+  </si>
+  <si>
+    <t>El sistema actualiza correctamente la información del paciente y muestra un mensaje de confirmación.</t>
+  </si>
+  <si>
+    <t>1. Acceder al módulo Pacientes.
+2. Escribir el nombre del paciente en el buscador.
+3. Presionar Buscar.</t>
+  </si>
+  <si>
+    <t>El sistema muestra el paciente correspondiente al nombre ingresado.</t>
+  </si>
+  <si>
+    <t>Debe existir un paciente registrado con el mismo DNI.</t>
+  </si>
+  <si>
+    <t>1. Acceder al módulo Pacientes.
+2. Presionar Nuevo Paciente.
+3. Completar el formulario utilizando un DNI ya registrado.
+4. Presionar Guardar.</t>
+  </si>
+  <si>
+    <t>El sistema impide el registro e informa que el DNI ya se encuentra registrado.</t>
+  </si>
+  <si>
+    <t>El paciente no debe existir.</t>
+  </si>
+  <si>
+    <t>1. Buscar un paciente inexistente.
+2. Intentar acceder a la edición mediante una URL o identificador inexistente.</t>
+  </si>
+  <si>
+    <t>El sistema informa que el paciente no existe y no permite modificar información.</t>
+  </si>
+  <si>
+    <t>1. Acceder al módulo Pacientes.
+2. Buscar un nombre inexistente.</t>
+  </si>
+  <si>
+    <t>El sistema informa que no se encontraron resultados.</t>
+  </si>
+  <si>
+    <t>No aplica.</t>
+  </si>
+  <si>
+    <t>1. Acceder al módulo Pacientes.
+2. Completar todos los datos excepto Nombre.
+3. Presionar Guardar.</t>
+  </si>
+  <si>
+    <t>El sistema informa que el campo Nombre es obligatorio y no registra el paciente.</t>
+  </si>
+  <si>
+    <t>1. Acceder al módulo Pacientes.
+2. Completar todos los datos excepto Apellido.
+3. Presionar Guardar.</t>
+  </si>
+  <si>
+    <t>El sistema informa que el campo Apellido es obligatorio y no registra el paciente.</t>
+  </si>
+  <si>
+    <t>1. Acceder al módulo Pacientes.
+2. Completar todos los datos excepto DNI.
+3. Presionar Guardar.</t>
+  </si>
+  <si>
+    <t>El sistema informa que el campo DNI es obligatorio y no registra el paciente.</t>
+  </si>
+  <si>
+    <t>1. Acceder al módulo Pacientes.
+2. Ingresar un correo con formato inválido (ejemplo: lucasgmail.com).
+3. Completar el resto de los datos correctamente.
+4. Presionar Guardar.</t>
+  </si>
+  <si>
+    <t>El sistema valida el formato del correo electrónico y solicita ingresar una dirección válida.</t>
+  </si>
+  <si>
+    <t>1. Acceder al módulo Pacientes.
+2. Ingresar un DNI con más caracteres de los permitidos.
+3. Completar el resto del formulario.
+4. Presionar Guardar.</t>
+  </si>
+  <si>
+    <t>El sistema valida la longitud del DNI e impide el registro.</t>
+  </si>
+  <si>
+    <t>1. Acceder al módulo Pacientes.
+2. Buscar un paciente existente.
+3. Presionar Eliminar.
+4. Confirmar la eliminación.</t>
+  </si>
+  <si>
+    <t>El sistema elimina el paciente y muestra un mensaje de confirmación.</t>
+  </si>
+  <si>
+    <t>1. Acceder al formulario de alta de pacientes.
+2. Verificar los campos obligatorios.</t>
+  </si>
+  <si>
+    <t>Los campos obligatorios aparecen correctamente identificados (por ejemplo, con un asterisco (*) o indicación visual).</t>
+  </si>
+  <si>
+    <t>1. Registrar un paciente con datos válidos.
+2. Presionar Guardar.</t>
+  </si>
+  <si>
+    <t>El sistema muestra un mensaje de confirmación indicando que el paciente fue registrado correctamente.</t>
+  </si>
+  <si>
+    <t>1. Eliminar un paciente existente.
+2. Confirmar la operación.</t>
+  </si>
+  <si>
+    <t>El sistema muestra un mensaje confirmando que el paciente fue eliminado correctamente.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -282,6 +386,12 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -644,19 +754,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E8466FE1-7E28-48DA-8E36-02C6BF23D7A6}">
-  <dimension ref="A1:J25"/>
+  <dimension ref="A1:J31"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.7109375" customWidth="1"/>
     <col min="2" max="2" width="19" customWidth="1"/>
-    <col min="3" max="3" width="39.7109375" customWidth="1"/>
+    <col min="3" max="3" width="42.5703125" customWidth="1"/>
     <col min="5" max="5" width="33.42578125" customWidth="1"/>
     <col min="6" max="6" width="33" customWidth="1"/>
     <col min="7" max="7" width="59.42578125" customWidth="1"/>
     <col min="8" max="8" width="11.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="3"/>
       <c r="B1" s="4" t="s">
         <v>0</v>
@@ -694,7 +804,7 @@
         <v>4</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>72</v>
+        <v>37</v>
       </c>
       <c r="D3" s="2"/>
       <c r="E3" s="2"/>
@@ -720,7 +830,7 @@
       <c r="I4" s="2"/>
       <c r="J4" s="2"/>
     </row>
-    <row r="5" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="2"/>
       <c r="B5" s="1" t="s">
         <v>7</v>
@@ -742,7 +852,7 @@
         <v>9</v>
       </c>
       <c r="C6" s="5">
-        <v>46234</v>
+        <v>46236</v>
       </c>
       <c r="D6" s="2"/>
       <c r="E6" s="2"/>
@@ -820,350 +930,394 @@
         <v>19</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" ht="90" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>20</v>
+        <v>54</v>
       </c>
       <c r="B11" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D11" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C11" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E11" s="1"/>
+      <c r="E11" s="1" t="s">
+        <v>62</v>
+      </c>
       <c r="F11" s="1" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>23</v>
+        <v>64</v>
       </c>
       <c r="H11" s="1"/>
       <c r="I11" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="75" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>20</v>
+        <v>54</v>
       </c>
       <c r="B12" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C12" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C12" s="1" t="s">
-        <v>58</v>
-      </c>
       <c r="D12" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E12" s="1"/>
-      <c r="F12" s="1"/>
+        <v>21</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>66</v>
+      </c>
       <c r="G12" s="1" t="s">
-        <v>27</v>
+        <v>67</v>
       </c>
       <c r="H12" s="1"/>
       <c r="I12" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>28</v>
+        <v>54</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E13" s="1"/>
+        <v>21</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>65</v>
+      </c>
       <c r="F13" s="1" t="s">
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>29</v>
+        <v>69</v>
       </c>
       <c r="H13" s="1"/>
       <c r="I13" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="J13" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" ht="75" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D14" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="J13" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" ht="45" x14ac:dyDescent="0.25">
-      <c r="A14" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="E14" s="1"/>
-      <c r="F14" s="1"/>
+      <c r="E14" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>71</v>
+      </c>
       <c r="G14" s="1" t="s">
-        <v>32</v>
+        <v>72</v>
       </c>
       <c r="H14" s="1"/>
       <c r="I14" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="J14" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D15" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="J14" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A15" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="E15" s="1"/>
-      <c r="F15" s="1"/>
+      <c r="E15" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>74</v>
+      </c>
       <c r="G15" s="1" t="s">
-        <v>27</v>
+        <v>75</v>
       </c>
       <c r="H15" s="1"/>
       <c r="I15" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>20</v>
+        <v>54</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>62</v>
+        <v>30</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E16" s="1"/>
-      <c r="F16" s="1"/>
+        <v>24</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>76</v>
+      </c>
       <c r="G16" s="1" t="s">
-        <v>35</v>
+        <v>77</v>
       </c>
       <c r="H16" s="1"/>
       <c r="I16" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>20</v>
+        <v>55</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>63</v>
+        <v>31</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E17" s="1"/>
-      <c r="F17" s="1"/>
+        <v>21</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>79</v>
+      </c>
       <c r="G17" s="1" t="s">
-        <v>37</v>
+        <v>80</v>
       </c>
       <c r="H17" s="1"/>
       <c r="I17" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>20</v>
+        <v>55</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>64</v>
+        <v>32</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E18" s="1"/>
-      <c r="F18" s="1"/>
+        <v>21</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>81</v>
+      </c>
       <c r="G18" s="1" t="s">
-        <v>39</v>
+        <v>82</v>
       </c>
       <c r="H18" s="1"/>
       <c r="I18" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J18" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>20</v>
+        <v>55</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>65</v>
+        <v>33</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E19" s="1"/>
+        <v>21</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>78</v>
+      </c>
       <c r="F19" s="1" t="s">
-        <v>56</v>
+        <v>83</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>41</v>
+        <v>84</v>
       </c>
       <c r="H19" s="1"/>
       <c r="I19" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J19" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" ht="105" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>20</v>
+        <v>55</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>66</v>
+        <v>34</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E20" s="1"/>
-      <c r="F20" s="1"/>
+        <v>21</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>85</v>
+      </c>
       <c r="G20" s="1" t="s">
-        <v>43</v>
+        <v>86</v>
       </c>
       <c r="H20" s="1"/>
       <c r="I20" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="J20" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" ht="90" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D21" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="J20" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" ht="45" x14ac:dyDescent="0.25">
-      <c r="A21" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="E21" s="1"/>
+      <c r="E21" s="1" t="s">
+        <v>78</v>
+      </c>
       <c r="F21" s="1" t="s">
-        <v>54</v>
+        <v>87</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>45</v>
+        <v>88</v>
       </c>
       <c r="H21" s="1"/>
       <c r="I21" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="J21" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D22" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="J21" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" ht="45" x14ac:dyDescent="0.25">
-      <c r="A22" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="E22" s="1"/>
-      <c r="F22" s="1"/>
+      <c r="E22" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>89</v>
+      </c>
       <c r="G22" s="1" t="s">
-        <v>47</v>
+        <v>90</v>
       </c>
       <c r="H22" s="1"/>
       <c r="I22" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J22" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="23" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>20</v>
+        <v>55</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>69</v>
+        <v>56</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E23" s="1"/>
-      <c r="F23" s="1"/>
+        <v>38</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>91</v>
+      </c>
       <c r="G23" s="1" t="s">
-        <v>49</v>
+        <v>92</v>
       </c>
       <c r="H23" s="1"/>
       <c r="I23" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J23" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="24" spans="1:10" ht="45" x14ac:dyDescent="0.25">
@@ -1171,54 +1325,87 @@
         <v>20</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E24" s="1"/>
-      <c r="F24" s="1"/>
+        <v>24</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>93</v>
+      </c>
       <c r="G24" s="1" t="s">
-        <v>51</v>
+        <v>94</v>
       </c>
       <c r="H24" s="1"/>
       <c r="I24" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J24" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>20</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>71</v>
+        <v>58</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E25" s="1"/>
-      <c r="F25" s="1"/>
+        <v>24</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>95</v>
+      </c>
       <c r="G25" s="1" t="s">
-        <v>53</v>
+        <v>96</v>
       </c>
       <c r="H25" s="1"/>
       <c r="I25" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J25" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A29" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>54</v>
+      </c>
+      <c r="C30" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>55</v>
+      </c>
+      <c r="C31" t="s">
+        <v>61</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I11:I25" xr:uid="{5C3DF877-8BF9-45CE-82CE-C803113304E5}">
       <formula1>"Pendiente, En ejecución, Aprobado, Falló, Bloqueado"</formula1>
